--- a/public/sap-reporting/expansion-150-downloads/EXT-PP10-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-PP10-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R5eb5e3ded6424448"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R83af165c5d474d7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R5bb1cb9e1c7843b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R620c2fede1234d51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rf8a81b256c2e4893"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R7755176088c44beb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -503,7 +503,7 @@
         <x:v>0000100001</x:v>
       </x:c>
       <x:c r="N7" s="2" t="str">
-        <x:v>0000100001</x:v>
+        <x:v>100.00</x:v>
       </x:c>
       <x:c r="O7" s="2" t="str">
         <x:v>0000100001</x:v>
@@ -554,7 +554,7 @@
         <x:v>0000100002</x:v>
       </x:c>
       <x:c r="N8" s="2" t="str">
-        <x:v>0000100002</x:v>
+        <x:v>125.00</x:v>
       </x:c>
       <x:c r="O8" s="2" t="str">
         <x:v>0000100002</x:v>
@@ -607,7 +607,7 @@
         <x:v>0000100003</x:v>
       </x:c>
       <x:c r="N9" s="2" t="str">
-        <x:v>0000100003</x:v>
+        <x:v>1.234,50</x:v>
       </x:c>
       <x:c r="O9" s="2" t="str">
         <x:v>0000100003</x:v>
@@ -660,7 +660,7 @@
         <x:v>0000100004</x:v>
       </x:c>
       <x:c r="N10" s="2" t="str">
-        <x:v>0000100004</x:v>
+        <x:v>175.00</x:v>
       </x:c>
       <x:c r="O10" s="2" t="str">
         <x:v>0000100004</x:v>
@@ -804,7 +804,7 @@
         <x:v>0000100001</x:v>
       </x:c>
       <x:c r="N2" s="2" t="str">
-        <x:v>0000100001</x:v>
+        <x:v>100.00</x:v>
       </x:c>
       <x:c r="O2" s="2" t="str">
         <x:v>0000100001</x:v>
@@ -855,7 +855,7 @@
         <x:v>0000100002</x:v>
       </x:c>
       <x:c r="N3" s="2" t="str">
-        <x:v>0000100002</x:v>
+        <x:v>125.00</x:v>
       </x:c>
       <x:c r="O3" s="2" t="str">
         <x:v>0000100002</x:v>
@@ -908,7 +908,7 @@
         <x:v>0000100003</x:v>
       </x:c>
       <x:c r="N4" s="2" t="str">
-        <x:v>0000100003</x:v>
+        <x:v>1.234,50</x:v>
       </x:c>
       <x:c r="O4" s="2" t="str">
         <x:v>0000100003</x:v>
@@ -961,7 +961,7 @@
         <x:v>0000100004</x:v>
       </x:c>
       <x:c r="N5" s="2" t="str">
-        <x:v>0000100004</x:v>
+        <x:v>175.00</x:v>
       </x:c>
       <x:c r="O5" s="2" t="str">
         <x:v>0000100004</x:v>
@@ -1273,7 +1273,7 @@
         <x:v>Giữ ID dạng Text và số0 đầu. Trim trên bản CLEAN riêng, giữ raw value và source-row lineage. Không join bằng tên diễn giải.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="63" customHeight="1">
+    <x:row r="15" ht="80" customHeight="1">
       <x:c r="A15" s="8" t="str">
         <x:v>14</x:v>
       </x:c>
@@ -1281,7 +1281,7 @@
         <x:v>Number of Capacities</x:v>
       </x:c>
       <x:c r="C15" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>raw_decimal</x:v>
       </x:c>
       <x:c r="D15" s="8" t="str">
         <x:v>Thuộc tính nghiệp vụ: Number of Capacities. Đọc tại grain của hồ sơ; nhãn và semantics cần đối chiếu hệ công ty.</x:v>
@@ -1290,7 +1290,7 @@
         <x:v>SAVA_PROPOSED / chưa xác minh</x:v>
       </x:c>
       <x:c r="F15" s="8" t="str">
-        <x:v>Giữ ID dạng Text và số0 đầu. Trim trên bản CLEAN riêng, giữ raw value và source-row lineage. Không join bằng tên diễn giải.</x:v>
+        <x:v>Giữ chuỗi RAW và locale. Chuẩn hóa dấu, separator, currency/UoM/price unit trước tính. Blank không là0; không cộng tỷ lệ/đơn giá/snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="63" customHeight="1">
